--- a/UCC1424x-Q1_Calculator_V8.xlsx
+++ b/UCC1424x-Q1_Calculator_V8.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB242E9-4324-494D-B906-975DA1CC520B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B85121FC-272C-462F-A017-8810EE8F7F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-7656" yWindow="-17388" windowWidth="30936" windowHeight="16896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dual Output" sheetId="17" r:id="rId1"/>
@@ -586,7 +586,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="130">
   <si>
     <t>mA</t>
   </si>
@@ -2720,6 +2720,12 @@
   <si>
     <t>Note (2): The maximum recommended average power SOA area at each Vin is determined by the lower value of the 2.0W limit (dotted line) and the corresponding thermal derating curve (solid line) at that input voltage. 
 The part is not recommeded to operate at an ambient temperature higher than 125 deg C.</t>
+  </si>
+  <si>
+    <t>2.2uF per driver</t>
+  </si>
+  <si>
+    <t>470n per driver</t>
   </si>
 </sst>
 </file>
@@ -3973,6 +3979,106 @@
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="43" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="5" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="50" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="46" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="39" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="6" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -3989,10 +4095,6 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="43" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="44" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -4139,18 +4241,6 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -4163,88 +4253,12 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="46" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="39" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="5" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="50" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4257,14 +4271,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="36" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -4454,8 +4460,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="15408419" y="9334499"/>
-          <a:ext cx="6837640" cy="15869568"/>
+          <a:off x="15401084" y="9361393"/>
+          <a:ext cx="6829490" cy="15858159"/>
           <a:chOff x="15947570" y="11375571"/>
           <a:chExt cx="7081703" cy="15683707"/>
         </a:xfrm>
@@ -4845,8 +4851,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="14959589" y="2852592"/>
-          <a:ext cx="28435298" cy="6145213"/>
+          <a:off x="14957144" y="2850962"/>
+          <a:ext cx="28256004" cy="6172107"/>
           <a:chOff x="23187025" y="12122149"/>
           <a:chExt cx="29340173" cy="6383338"/>
         </a:xfrm>
@@ -7036,12 +7042,12 @@
   <sheetData>
     <row r="1" spans="1:23" ht="30.6" thickBot="1">
       <c r="A1" s="16"/>
-      <c r="B1" s="103" t="s">
+      <c r="B1" s="128" t="s">
         <v>119</v>
       </c>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
       <c r="F1" s="16"/>
       <c r="G1" s="37"/>
       <c r="H1" s="16"/>
@@ -7057,12 +7063,12 @@
     </row>
     <row r="2" spans="1:23" ht="15.6">
       <c r="A2" s="16"/>
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="129" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="106"/>
+      <c r="C2" s="130"/>
+      <c r="D2" s="130"/>
+      <c r="E2" s="131"/>
       <c r="F2" s="16"/>
       <c r="G2" s="37"/>
       <c r="H2" s="16"/>
@@ -7078,12 +7084,12 @@
     </row>
     <row r="3" spans="1:23">
       <c r="A3" s="16"/>
-      <c r="B3" s="107" t="s">
+      <c r="B3" s="132" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="109"/>
+      <c r="C3" s="133"/>
+      <c r="D3" s="133"/>
+      <c r="E3" s="134"/>
       <c r="F3" s="16"/>
       <c r="G3" s="37"/>
       <c r="H3" s="16"/>
@@ -7099,10 +7105,10 @@
     </row>
     <row r="4" spans="1:23">
       <c r="A4" s="17"/>
-      <c r="B4" s="107"/>
-      <c r="C4" s="108"/>
-      <c r="D4" s="108"/>
-      <c r="E4" s="109"/>
+      <c r="B4" s="132"/>
+      <c r="C4" s="133"/>
+      <c r="D4" s="133"/>
+      <c r="E4" s="134"/>
       <c r="F4" s="16"/>
       <c r="G4" s="37"/>
       <c r="H4" s="16"/>
@@ -7118,10 +7124,10 @@
     </row>
     <row r="5" spans="1:23">
       <c r="A5" s="17"/>
-      <c r="B5" s="107"/>
-      <c r="C5" s="108"/>
-      <c r="D5" s="108"/>
-      <c r="E5" s="109"/>
+      <c r="B5" s="132"/>
+      <c r="C5" s="133"/>
+      <c r="D5" s="133"/>
+      <c r="E5" s="134"/>
       <c r="F5" s="18"/>
       <c r="G5" s="37"/>
       <c r="H5" s="16"/>
@@ -7137,10 +7143,10 @@
     </row>
     <row r="6" spans="1:23" ht="15" thickBot="1">
       <c r="A6" s="17"/>
-      <c r="B6" s="110"/>
-      <c r="C6" s="111"/>
-      <c r="D6" s="111"/>
-      <c r="E6" s="112"/>
+      <c r="B6" s="135"/>
+      <c r="C6" s="136"/>
+      <c r="D6" s="136"/>
+      <c r="E6" s="137"/>
       <c r="F6" s="18"/>
       <c r="G6" s="37"/>
       <c r="H6" s="16"/>
@@ -7156,12 +7162,12 @@
     </row>
     <row r="7" spans="1:23" ht="25.35" customHeight="1">
       <c r="A7" s="17"/>
-      <c r="B7" s="113" t="s">
+      <c r="B7" s="138" t="s">
         <v>120</v>
       </c>
-      <c r="C7" s="114"/>
-      <c r="D7" s="114"/>
-      <c r="E7" s="115"/>
+      <c r="C7" s="139"/>
+      <c r="D7" s="139"/>
+      <c r="E7" s="140"/>
       <c r="F7" s="18"/>
       <c r="G7" s="37"/>
       <c r="H7" s="16"/>
@@ -7177,12 +7183,12 @@
     </row>
     <row r="8" spans="1:23" ht="17.399999999999999">
       <c r="A8" s="17"/>
-      <c r="B8" s="116" t="s">
+      <c r="B8" s="141" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="117"/>
-      <c r="D8" s="117"/>
-      <c r="E8" s="118"/>
+      <c r="C8" s="142"/>
+      <c r="D8" s="142"/>
+      <c r="E8" s="143"/>
       <c r="F8" s="18"/>
       <c r="G8" s="37"/>
       <c r="H8" s="16"/>
@@ -7198,12 +7204,12 @@
     </row>
     <row r="9" spans="1:23" ht="18" thickBot="1">
       <c r="A9" s="17"/>
-      <c r="B9" s="100" t="s">
+      <c r="B9" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="101"/>
-      <c r="D9" s="101"/>
-      <c r="E9" s="102"/>
+      <c r="C9" s="126"/>
+      <c r="D9" s="126"/>
+      <c r="E9" s="127"/>
       <c r="F9" s="18"/>
       <c r="G9" s="37"/>
       <c r="H9" s="16"/>
@@ -7219,12 +7225,12 @@
     </row>
     <row r="10" spans="1:23" ht="56.25" customHeight="1" thickBot="1">
       <c r="A10" s="17"/>
-      <c r="B10" s="119" t="s">
+      <c r="B10" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="120"/>
-      <c r="D10" s="120"/>
-      <c r="E10" s="121"/>
+      <c r="C10" s="145"/>
+      <c r="D10" s="145"/>
+      <c r="E10" s="146"/>
       <c r="F10" s="16"/>
       <c r="G10" s="37"/>
       <c r="H10" s="16"/>
@@ -7240,12 +7246,12 @@
     </row>
     <row r="11" spans="1:23">
       <c r="A11" s="17"/>
-      <c r="B11" s="122" t="s">
+      <c r="B11" s="147" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="123"/>
-      <c r="D11" s="123"/>
-      <c r="E11" s="124"/>
+      <c r="C11" s="148"/>
+      <c r="D11" s="148"/>
+      <c r="E11" s="149"/>
       <c r="F11" s="16"/>
       <c r="G11" s="37"/>
       <c r="H11" s="16"/>
@@ -7261,10 +7267,10 @@
     </row>
     <row r="12" spans="1:23" ht="15" thickBot="1">
       <c r="A12" s="17"/>
-      <c r="B12" s="125"/>
-      <c r="C12" s="126"/>
-      <c r="D12" s="126"/>
-      <c r="E12" s="127"/>
+      <c r="B12" s="150"/>
+      <c r="C12" s="151"/>
+      <c r="D12" s="151"/>
+      <c r="E12" s="152"/>
       <c r="F12" s="16"/>
       <c r="G12" s="37"/>
       <c r="H12" s="16"/>
@@ -7313,7 +7319,7 @@
         <v>18</v>
       </c>
       <c r="C14" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" s="92" t="s">
         <v>6</v>
@@ -7325,7 +7331,7 @@
       <c r="F14" s="16"/>
       <c r="G14" s="37">
         <f>VDD_VEE-COM_VEE</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H14" s="16" t="s">
         <v>84</v>
@@ -7355,7 +7361,7 @@
       <c r="F15" s="16"/>
       <c r="G15" s="37">
         <f>G14*PERCENT_VPP_MAX/100</f>
-        <v>0.16500000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="H15" s="16" t="s">
         <v>87</v>
@@ -7401,7 +7407,8 @@
         <v>30</v>
       </c>
       <c r="C17" s="5">
-        <v>0</v>
+        <f>4.4*4</f>
+        <v>17.600000000000001</v>
       </c>
       <c r="D17" s="24" t="s">
         <v>0</v>
@@ -7428,7 +7435,7 @@
         <v>31</v>
       </c>
       <c r="C18" s="6">
-        <v>0</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="D18" s="24" t="s">
         <v>0</v>
@@ -7478,7 +7485,7 @@
         <v>60</v>
       </c>
       <c r="C20" s="5">
-        <v>0</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="D20" s="24" t="s">
         <v>0</v>
@@ -7504,7 +7511,7 @@
       </c>
       <c r="C21" s="42">
         <f>IQ_DRIVER_VDD+IQ_OTHER_VDD</f>
-        <v>0</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="D21" s="24" t="s">
         <v>0</v>
@@ -7530,7 +7537,7 @@
       </c>
       <c r="C22" s="42">
         <f>IQ_DRIVER_VEE+IQ_OTHER_VEE</f>
-        <v>0</v>
+        <v>27.3</v>
       </c>
       <c r="D22" s="24" t="s">
         <v>0</v>
@@ -7581,7 +7588,7 @@
         <v>COM_VEE &gt; 2.5V: Bottom feedback resistor between FBVEE and VEE, RFBVEE_VEE</v>
       </c>
       <c r="C24" s="5">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D24" s="88" t="s">
         <v>13</v>
@@ -7729,23 +7736,23 @@
     </row>
     <row r="30" spans="1:17" ht="20.100000000000001" customHeight="1">
       <c r="A30" s="17"/>
-      <c r="B30" s="128" t="s">
+      <c r="B30" s="153" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="130">
+      <c r="C30" s="155">
         <f>IF(ABS(G30)&gt;ABS(G31), G30,G31)</f>
-        <v>-0.46269481132405271</v>
-      </c>
-      <c r="D30" s="132" t="s">
+        <v>-0.67368421052631566</v>
+      </c>
+      <c r="D30" s="157" t="s">
         <v>0</v>
       </c>
-      <c r="E30" s="134" t="s">
+      <c r="E30" s="159" t="s">
         <v>38</v>
       </c>
       <c r="F30" s="16"/>
       <c r="G30" s="37">
         <f>10^3*(Qgtot*fsw*10^-3*(((COUT3*(1+dCOUT3_POS*0.01)/(COUT2*(1+dCOUT2_NEG*0.01)+COUT3*(1+dCOUT3_POS*0.01))))-(COUT3/(COUT2+COUT3))))</f>
-        <v>0.3807222538646961</v>
+        <v>0.60952380952380947</v>
       </c>
       <c r="H30" s="16" t="s">
         <v>0</v>
@@ -7764,14 +7771,14 @@
     </row>
     <row r="31" spans="1:17" ht="20.100000000000001" customHeight="1">
       <c r="A31" s="17"/>
-      <c r="B31" s="129"/>
-      <c r="C31" s="131"/>
-      <c r="D31" s="133"/>
-      <c r="E31" s="135"/>
+      <c r="B31" s="154"/>
+      <c r="C31" s="156"/>
+      <c r="D31" s="158"/>
+      <c r="E31" s="160"/>
       <c r="F31" s="16"/>
       <c r="G31" s="37">
         <f>-10^3*(Qgtot*fsw*10^-3*(((COUT2*(1+dCOUT2_POS*0.01)/(COUT2*(1+dCOUT2_POS*0.01)+COUT3*(1+dCOUT3_NEG*0.01))))-(COUT2/(COUT2+COUT3))))</f>
-        <v>-0.46269481132405271</v>
+        <v>-0.67368421052631566</v>
       </c>
       <c r="H31" s="16" t="s">
         <v>0</v>
@@ -7790,23 +7797,23 @@
     </row>
     <row r="32" spans="1:17" ht="20.100000000000001" customHeight="1">
       <c r="A32" s="17"/>
-      <c r="B32" s="152" t="s">
+      <c r="B32" s="102" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="154">
+      <c r="C32" s="104">
         <f>IF(ABS(G32)&gt;ABS(G33), G32, G33)</f>
-        <v>-0.46269481132405271</v>
-      </c>
-      <c r="D32" s="156" t="s">
+        <v>10.309523809523808</v>
+      </c>
+      <c r="D32" s="106" t="s">
         <v>0</v>
       </c>
-      <c r="E32" s="158" t="s">
+      <c r="E32" s="108" t="s">
         <v>38</v>
       </c>
       <c r="F32" s="16"/>
       <c r="G32" s="37">
         <f>G30+IF(I_COM_VEE&gt;I_VDD_COM, I_COM_VEE-I_VDD_COM,0)</f>
-        <v>0.3807222538646961</v>
+        <v>10.309523809523808</v>
       </c>
       <c r="H32" s="16" t="s">
         <v>0</v>
@@ -7825,14 +7832,14 @@
     </row>
     <row r="33" spans="1:17" ht="20.100000000000001" customHeight="1">
       <c r="A33" s="17"/>
-      <c r="B33" s="153"/>
-      <c r="C33" s="155"/>
-      <c r="D33" s="157"/>
-      <c r="E33" s="159"/>
+      <c r="B33" s="103"/>
+      <c r="C33" s="105"/>
+      <c r="D33" s="107"/>
+      <c r="E33" s="109"/>
       <c r="F33" s="16"/>
       <c r="G33" s="82">
         <f>G31-IF(I_COM_VEE&lt;I_VDD_COM, I_VDD_COM-I_COM_VEE,0)</f>
-        <v>-0.46269481132405271</v>
+        <v>-0.67368421052631566</v>
       </c>
       <c r="H33" s="16" t="s">
         <v>0</v>
@@ -7882,7 +7889,7 @@
       </c>
       <c r="C35" s="45">
         <f>IF(ABS(IQ_DRIVER_VDD)&gt;ABS(IQ_DRIVER_VEE), VDD_VEE*IQ_DRIVER_VDD*0.001,VDD_VEE*IQ_DRIVER_VEE*0.001)</f>
-        <v>0</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="D35" s="24" t="s">
         <v>34</v>
@@ -7961,7 +7968,7 @@
       </c>
       <c r="C38" s="47">
         <f>C34+C35+C36</f>
-        <v>0.14400000000000002</v>
+        <v>0.40800000000000003</v>
       </c>
       <c r="D38" s="20" t="s">
         <v>34</v>
@@ -7988,7 +7995,7 @@
         <v>56</v>
       </c>
       <c r="C39" s="12">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="D39" s="41" t="s">
         <v>34</v>
@@ -7999,7 +8006,7 @@
       <c r="F39" s="16"/>
       <c r="G39" s="37">
         <f>P_MAX/VDD_VEE</f>
-        <v>0.2</v>
+        <v>0.18666666666666665</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>59</v>
@@ -8023,7 +8030,7 @@
       </c>
       <c r="C40" s="48">
         <f>P_MAX/VDD_VEE</f>
-        <v>0.2</v>
+        <v>0.18666666666666665</v>
       </c>
       <c r="D40" s="28" t="s">
         <v>59</v>
@@ -8063,12 +8070,12 @@
     </row>
     <row r="42" spans="1:17">
       <c r="A42" s="17"/>
-      <c r="B42" s="136" t="s">
+      <c r="B42" s="110" t="s">
         <v>25</v>
       </c>
-      <c r="C42" s="137"/>
-      <c r="D42" s="137"/>
-      <c r="E42" s="138"/>
+      <c r="C42" s="111"/>
+      <c r="D42" s="111"/>
+      <c r="E42" s="112"/>
       <c r="F42" s="16"/>
       <c r="G42" s="37"/>
       <c r="H42" s="16"/>
@@ -8084,10 +8091,10 @@
     </row>
     <row r="43" spans="1:17" ht="15" thickBot="1">
       <c r="A43" s="17"/>
-      <c r="B43" s="160"/>
-      <c r="C43" s="161"/>
-      <c r="D43" s="161"/>
-      <c r="E43" s="162"/>
+      <c r="B43" s="113"/>
+      <c r="C43" s="114"/>
+      <c r="D43" s="114"/>
+      <c r="E43" s="115"/>
       <c r="F43" s="16"/>
       <c r="G43" s="37"/>
       <c r="H43" s="16"/>
@@ -8103,12 +8110,12 @@
     </row>
     <row r="44" spans="1:17" ht="24.75" customHeight="1">
       <c r="A44" s="17"/>
-      <c r="B44" s="142" t="s">
+      <c r="B44" s="116" t="s">
         <v>91</v>
       </c>
-      <c r="C44" s="143"/>
-      <c r="D44" s="143"/>
-      <c r="E44" s="163"/>
+      <c r="C44" s="117"/>
+      <c r="D44" s="117"/>
+      <c r="E44" s="119"/>
       <c r="F44" s="16"/>
       <c r="G44" s="37"/>
       <c r="H44" s="16"/>
@@ -8156,7 +8163,7 @@
       </c>
       <c r="C46" s="86">
         <f>IF(COM_VEE&lt;2.5,R_4*(2.5-COM_VEE)/(VDD_VEE-2.5),(IF(COM_VEE&gt;2.5,R_4*(COM_VEE-2.5)/2.5,R_4)))</f>
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D46" s="88" t="s">
         <v>13</v>
@@ -8177,12 +8184,12 @@
     </row>
     <row r="47" spans="1:17" ht="24.75" customHeight="1">
       <c r="A47" s="17"/>
-      <c r="B47" s="142" t="s">
+      <c r="B47" s="116" t="s">
         <v>92</v>
       </c>
-      <c r="C47" s="143"/>
-      <c r="D47" s="143"/>
-      <c r="E47" s="144"/>
+      <c r="C47" s="117"/>
+      <c r="D47" s="117"/>
+      <c r="E47" s="118"/>
       <c r="F47" s="16"/>
       <c r="G47" s="37"/>
       <c r="H47" s="16"/>
@@ -8203,7 +8210,7 @@
       </c>
       <c r="C48" s="43">
         <f>10^6*(G50*(Qgtot/10^6)*(G50^3+SQRT(G51)+G50^2*SQRT(G51)-1))/(G15*(G50+1)^2*G51)</f>
-        <v>0.81460763513297429</v>
+        <v>0.64737194852550561</v>
       </c>
       <c r="D48" s="39" t="s">
         <v>82</v>
@@ -8228,7 +8235,7 @@
         <v>90</v>
       </c>
       <c r="C49" s="14">
-        <v>20</v>
+        <v>0.65</v>
       </c>
       <c r="D49" s="24" t="s">
         <v>82</v>
@@ -8236,7 +8243,9 @@
       <c r="E49" s="60" t="s">
         <v>107</v>
       </c>
-      <c r="F49" s="16"/>
+      <c r="F49" s="16" t="s">
+        <v>128</v>
+      </c>
       <c r="G49" s="37"/>
       <c r="H49" s="16"/>
       <c r="I49" s="16"/>
@@ -8256,7 +8265,7 @@
       </c>
       <c r="C50" s="43">
         <f>(G50*Qgtot-(1+G50)*C49*G15+SQRT(C49^2*G15^2*(G50^2+2*G50+1)+2*C49*G50*Qgtot*G15*(1-G50)+G50^2*Qgtot^2))/(2*G50*G15)</f>
-        <v>0.26544025492221024</v>
+        <v>0.64344465865048572</v>
       </c>
       <c r="D50" s="24" t="s">
         <v>9</v>
@@ -8265,7 +8274,7 @@
       <c r="F50" s="16"/>
       <c r="G50" s="37">
         <f>(G14*(G39-I_COM_VEE/1000))/(COM_VEE*(G39-I_VDD_COM/1000))</f>
-        <v>2.75</v>
+        <v>1.8852523659305993</v>
       </c>
       <c r="I50" s="16" t="s">
         <v>83</v>
@@ -8285,7 +8294,7 @@
         <v>113</v>
       </c>
       <c r="C51" s="14">
-        <v>4.7</v>
+        <v>0.65</v>
       </c>
       <c r="D51" s="24" t="s">
         <v>9</v>
@@ -8293,10 +8302,12 @@
       <c r="E51" s="60" t="s">
         <v>106</v>
       </c>
-      <c r="F51" s="16"/>
+      <c r="F51" s="16" t="s">
+        <v>129</v>
+      </c>
       <c r="G51" s="37">
         <f>G50^2+G50+1</f>
-        <v>11.3125</v>
+        <v>6.4394288491775216</v>
       </c>
       <c r="I51" s="16" t="s">
         <v>86</v>
@@ -8317,7 +8328,7 @@
       </c>
       <c r="C52" s="50">
         <f>COUT2*G50</f>
-        <v>12.925000000000001</v>
+        <v>1.2254140378548897</v>
       </c>
       <c r="D52" s="20" t="s">
         <v>9</v>
@@ -8342,7 +8353,7 @@
         <v>62</v>
       </c>
       <c r="C53" s="54">
-        <v>22</v>
+        <v>1.3</v>
       </c>
       <c r="D53" s="28" t="s">
         <v>9</v>
@@ -8350,7 +8361,9 @@
       <c r="E53" s="72" t="s">
         <v>105</v>
       </c>
-      <c r="F53" s="16"/>
+      <c r="F53" s="16" t="s">
+        <v>128</v>
+      </c>
       <c r="G53" s="37"/>
       <c r="H53" s="16"/>
       <c r="I53" s="16"/>
@@ -8365,12 +8378,12 @@
     </row>
     <row r="54" spans="1:17" ht="24.75" customHeight="1">
       <c r="A54" s="17"/>
-      <c r="B54" s="142" t="s">
+      <c r="B54" s="116" t="s">
         <v>93</v>
       </c>
-      <c r="C54" s="143"/>
-      <c r="D54" s="143"/>
-      <c r="E54" s="144"/>
+      <c r="C54" s="117"/>
+      <c r="D54" s="117"/>
+      <c r="E54" s="118"/>
       <c r="F54" s="16"/>
       <c r="G54" s="37"/>
       <c r="H54" s="16"/>
@@ -8386,21 +8399,21 @@
     </row>
     <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="17"/>
-      <c r="B55" s="150" t="s">
+      <c r="B55" s="100" t="s">
         <v>95</v>
       </c>
-      <c r="C55" s="148">
+      <c r="C55" s="98">
         <f>MIN(RLIM_UP,RLIM_DN, G57)</f>
-        <v>1155.7707509881423</v>
-      </c>
-      <c r="D55" s="145" t="s">
+        <v>-559.05387531963675</v>
+      </c>
+      <c r="D55" s="94" t="s">
         <v>17</v>
       </c>
-      <c r="E55" s="98"/>
+      <c r="E55" s="96"/>
       <c r="F55" s="16"/>
       <c r="G55" s="37">
         <f>((VDD_VEE-COM_VEE)/((COUT3*0.000001*(1+dCOUT3_POS*0.01)*(0.1*(COM_VEE))/0.003)+ABS(ILIM_UP*10^-3)))-30</f>
-        <v>2900.1643900830554</v>
+        <v>917.08714329202996</v>
       </c>
       <c r="H55" s="16" t="s">
         <v>17</v>
@@ -8419,14 +8432,14 @@
     </row>
     <row r="56" spans="1:17" ht="13.5" customHeight="1">
       <c r="A56" s="16"/>
-      <c r="B56" s="151"/>
-      <c r="C56" s="149"/>
-      <c r="D56" s="146"/>
-      <c r="E56" s="147"/>
+      <c r="B56" s="101"/>
+      <c r="C56" s="99"/>
+      <c r="D56" s="95"/>
+      <c r="E56" s="97"/>
       <c r="F56" s="16"/>
       <c r="G56" s="37">
         <f>(COM_VEE/ABS(ILIM_DN*10^-3))-30</f>
-        <v>8615.0072533849143</v>
+        <v>7391.8750000000009</v>
       </c>
       <c r="H56" s="16" t="s">
         <v>17</v>
@@ -8445,14 +8458,14 @@
     </row>
     <row r="57" spans="1:17" ht="13.5" customHeight="1">
       <c r="A57" s="16"/>
-      <c r="B57" s="151"/>
-      <c r="C57" s="149"/>
-      <c r="D57" s="146"/>
-      <c r="E57" s="147"/>
+      <c r="B57" s="101"/>
+      <c r="C57" s="99"/>
+      <c r="D57" s="95"/>
+      <c r="E57" s="97"/>
       <c r="F57" s="16"/>
       <c r="G57" s="37">
         <f>(COM_VEE/((COUT3*0.000001*(1+dCOUT3_POS*0.01)*(0.1*COM_VEE)/0.003)+(I_VDD_COM-I_COM_VEE)*0.001))-30</f>
-        <v>1155.7707509881423</v>
+        <v>-559.05387531963675</v>
       </c>
       <c r="H57" s="16" t="s">
         <v>17</v>
@@ -8475,7 +8488,7 @@
         <v>96</v>
       </c>
       <c r="C58" s="3">
-        <v>400</v>
+        <v>470</v>
       </c>
       <c r="D58" s="55" t="s">
         <v>17</v>
@@ -8503,7 +8516,7 @@
       </c>
       <c r="C59" s="62">
         <f>G14^2/C58*0.33+(ILIM_MAX*10^-3)^2*C58</f>
-        <v>9.9910634595370473E-2</v>
+        <v>0.12016731811164182</v>
       </c>
       <c r="D59" s="63" t="s">
         <v>34</v>
@@ -8526,12 +8539,12 @@
     </row>
     <row r="60" spans="1:17" ht="24.75" customHeight="1">
       <c r="A60" s="16"/>
-      <c r="B60" s="94" t="s">
+      <c r="B60" s="120" t="s">
         <v>94</v>
       </c>
-      <c r="C60" s="95"/>
-      <c r="D60" s="95"/>
-      <c r="E60" s="96"/>
+      <c r="C60" s="121"/>
+      <c r="D60" s="121"/>
+      <c r="E60" s="122"/>
       <c r="F60" s="16"/>
       <c r="G60" s="37"/>
       <c r="H60" s="16"/>
@@ -8552,7 +8565,7 @@
       </c>
       <c r="C61" s="78">
         <f>RLIM_UP</f>
-        <v>2900.1643900830554</v>
+        <v>917.08714329202996</v>
       </c>
       <c r="D61" s="55" t="s">
         <v>17</v>
@@ -8561,7 +8574,7 @@
       <c r="F61" s="16"/>
       <c r="G61" s="79">
         <f>COM_VEE/RLIM</f>
-        <v>1.6000000000000001E-3</v>
+        <v>5.5555555555555558E-3</v>
       </c>
       <c r="H61" s="1" t="s">
         <v>59</v>
@@ -8584,7 +8597,7 @@
         <v>97</v>
       </c>
       <c r="C62" s="3">
-        <v>2500</v>
+        <v>900</v>
       </c>
       <c r="D62" s="55" t="s">
         <v>17</v>
@@ -8593,9 +8606,9 @@
         <v>126</v>
       </c>
       <c r="F62" s="16"/>
-      <c r="G62" s="79">
+      <c r="G62" s="79" t="e">
         <f>(COM_VEE-0.5)/C65</f>
-        <v>7.7777777777777776E-3</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>59</v>
@@ -8617,9 +8630,9 @@
       <c r="B63" s="67" t="s">
         <v>98</v>
       </c>
-      <c r="C63" s="57">
+      <c r="C63" s="57" t="e">
         <f>(G14^2/RLIM)*0.33+(ILIM_DN/1000*G63)^2*RLIM</f>
-        <v>1.5987580068338558E-2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D63" s="56" t="s">
         <v>34</v>
@@ -8628,9 +8641,9 @@
         <v>99</v>
       </c>
       <c r="F63" s="16"/>
-      <c r="G63" s="80">
+      <c r="G63" s="80" t="e">
         <f>G61/(G61+G62)</f>
-        <v>0.17061611374407581</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="I63" s="16" t="s">
         <v>88</v>
@@ -8651,7 +8664,7 @@
       </c>
       <c r="C64" s="78">
         <f>(COM_VEE-0.5)/(COM_VEE*(1/MIN(RLIM_DN, G57)-1/RLIM_UP))</f>
-        <v>1681.3490157804677</v>
+        <v>-312.59276959249121</v>
       </c>
       <c r="D64" s="55" t="s">
         <v>17</v>
@@ -8675,9 +8688,7 @@
       <c r="B65" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="C65" s="3">
-        <v>450</v>
-      </c>
+      <c r="C65" s="3"/>
       <c r="D65" s="55" t="s">
         <v>17</v>
       </c>
@@ -8702,9 +8713,9 @@
       <c r="B66" s="61" t="s">
         <v>116</v>
       </c>
-      <c r="C66" s="62">
+      <c r="C66" s="62" t="e">
         <f>(ILIM_MAX*10^-3*G66)^2*C65</f>
-        <v>6.6269387898375555E-5</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D66" s="63" t="s">
         <v>34</v>
@@ -8713,9 +8724,9 @@
         <v>103</v>
       </c>
       <c r="F66" s="16"/>
-      <c r="G66" s="80">
+      <c r="G66" s="80" t="e">
         <f>G62/(G61+G62)</f>
-        <v>0.82938388625592407</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="I66" s="16" t="s">
         <v>88</v>
@@ -8750,12 +8761,12 @@
     </row>
     <row r="68" spans="1:17">
       <c r="A68" s="17"/>
-      <c r="B68" s="136" t="s">
+      <c r="B68" s="110" t="s">
         <v>27</v>
       </c>
-      <c r="C68" s="137"/>
-      <c r="D68" s="137"/>
-      <c r="E68" s="138"/>
+      <c r="C68" s="111"/>
+      <c r="D68" s="111"/>
+      <c r="E68" s="112"/>
       <c r="F68" s="16"/>
       <c r="G68" s="37"/>
       <c r="H68" s="16"/>
@@ -8771,10 +8782,10 @@
     </row>
     <row r="69" spans="1:17" ht="15" thickBot="1">
       <c r="A69" s="17"/>
-      <c r="B69" s="139"/>
-      <c r="C69" s="140"/>
-      <c r="D69" s="140"/>
-      <c r="E69" s="141"/>
+      <c r="B69" s="161"/>
+      <c r="C69" s="162"/>
+      <c r="D69" s="162"/>
+      <c r="E69" s="163"/>
       <c r="F69" s="16"/>
       <c r="G69" s="37"/>
       <c r="H69" s="16"/>
@@ -8799,7 +8810,7 @@
       <c r="D70" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="E70" s="97" t="s">
+      <c r="E70" s="123" t="s">
         <v>121</v>
       </c>
       <c r="F70" s="16"/>
@@ -8826,7 +8837,7 @@
       <c r="D71" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="E71" s="98"/>
+      <c r="E71" s="96"/>
       <c r="F71" s="16"/>
       <c r="G71" s="37"/>
       <c r="H71" s="16"/>
@@ -8851,7 +8862,7 @@
       <c r="D72" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="E72" s="98"/>
+      <c r="E72" s="96"/>
       <c r="F72" s="16"/>
       <c r="G72" s="37"/>
       <c r="H72" s="16"/>
@@ -8876,7 +8887,7 @@
       <c r="D73" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="E73" s="99"/>
+      <c r="E73" s="124"/>
       <c r="F73" s="16"/>
       <c r="G73" s="37"/>
       <c r="H73" s="16"/>
@@ -9053,17 +9064,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="Va3jEj82vDSI0RIn4l24guiZ58mS6gjCWiOqAxPYidVUCKqftc+17Huh/yqS+R7nHUe1+LP9Y8RJt2dfuTB77w==" saltValue="aQ6PxnToVlJW6VSphtHp0g==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="27">
-    <mergeCell ref="D55:D57"/>
-    <mergeCell ref="E55:E57"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="B42:E43"/>
-    <mergeCell ref="B54:E54"/>
-    <mergeCell ref="B44:E44"/>
     <mergeCell ref="B60:E60"/>
     <mergeCell ref="E70:E73"/>
     <mergeCell ref="B9:E9"/>
@@ -9080,6 +9080,17 @@
     <mergeCell ref="E30:E31"/>
     <mergeCell ref="B68:E69"/>
     <mergeCell ref="B47:E47"/>
+    <mergeCell ref="D55:D57"/>
+    <mergeCell ref="E55:E57"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="B42:E43"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="B44:E44"/>
   </mergeCells>
   <conditionalFormatting sqref="B13:B20 D13:E20">
     <cfRule type="expression" dxfId="18" priority="21">
@@ -9184,12 +9195,12 @@
   <sheetData>
     <row r="1" spans="1:23" ht="30.6" thickBot="1">
       <c r="A1" s="16"/>
-      <c r="B1" s="103" t="s">
+      <c r="B1" s="128" t="s">
         <v>123</v>
       </c>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
       <c r="F1" s="16"/>
       <c r="G1" s="16"/>
       <c r="H1" s="16"/>
@@ -9210,12 +9221,12 @@
     </row>
     <row r="2" spans="1:23" ht="15.6">
       <c r="A2" s="16"/>
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="129" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="106"/>
+      <c r="C2" s="130"/>
+      <c r="D2" s="130"/>
+      <c r="E2" s="131"/>
       <c r="F2" s="16"/>
       <c r="G2" s="16"/>
       <c r="H2" s="16"/>
@@ -9236,12 +9247,12 @@
     </row>
     <row r="3" spans="1:23">
       <c r="A3" s="16"/>
-      <c r="B3" s="107" t="s">
+      <c r="B3" s="132" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="109"/>
+      <c r="C3" s="133"/>
+      <c r="D3" s="133"/>
+      <c r="E3" s="134"/>
       <c r="F3" s="16"/>
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
@@ -9262,10 +9273,10 @@
     </row>
     <row r="4" spans="1:23">
       <c r="A4" s="17"/>
-      <c r="B4" s="107"/>
-      <c r="C4" s="108"/>
-      <c r="D4" s="108"/>
-      <c r="E4" s="109"/>
+      <c r="B4" s="132"/>
+      <c r="C4" s="133"/>
+      <c r="D4" s="133"/>
+      <c r="E4" s="134"/>
       <c r="F4" s="16"/>
       <c r="G4" s="16"/>
       <c r="H4" s="16"/>
@@ -9286,10 +9297,10 @@
     </row>
     <row r="5" spans="1:23">
       <c r="A5" s="17"/>
-      <c r="B5" s="107"/>
-      <c r="C5" s="108"/>
-      <c r="D5" s="108"/>
-      <c r="E5" s="109"/>
+      <c r="B5" s="132"/>
+      <c r="C5" s="133"/>
+      <c r="D5" s="133"/>
+      <c r="E5" s="134"/>
       <c r="F5" s="18"/>
       <c r="G5" s="16"/>
       <c r="H5" s="16"/>
@@ -9310,10 +9321,10 @@
     </row>
     <row r="6" spans="1:23" ht="15" thickBot="1">
       <c r="A6" s="17"/>
-      <c r="B6" s="110"/>
-      <c r="C6" s="111"/>
-      <c r="D6" s="111"/>
-      <c r="E6" s="112"/>
+      <c r="B6" s="135"/>
+      <c r="C6" s="136"/>
+      <c r="D6" s="136"/>
+      <c r="E6" s="137"/>
       <c r="F6" s="18"/>
       <c r="G6" s="16"/>
       <c r="H6" s="16"/>
@@ -9334,12 +9345,12 @@
     </row>
     <row r="7" spans="1:23" ht="25.35" customHeight="1">
       <c r="A7" s="17"/>
-      <c r="B7" s="113" t="s">
+      <c r="B7" s="138" t="s">
         <v>122</v>
       </c>
-      <c r="C7" s="114"/>
-      <c r="D7" s="114"/>
-      <c r="E7" s="115"/>
+      <c r="C7" s="139"/>
+      <c r="D7" s="139"/>
+      <c r="E7" s="140"/>
       <c r="F7" s="18"/>
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
@@ -9360,12 +9371,12 @@
     </row>
     <row r="8" spans="1:23" ht="17.399999999999999">
       <c r="A8" s="17"/>
-      <c r="B8" s="116" t="s">
+      <c r="B8" s="141" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="167"/>
-      <c r="D8" s="167"/>
-      <c r="E8" s="168"/>
+      <c r="C8" s="164"/>
+      <c r="D8" s="164"/>
+      <c r="E8" s="165"/>
       <c r="F8" s="18"/>
       <c r="G8" s="16"/>
       <c r="H8" s="16"/>
@@ -9386,12 +9397,12 @@
     </row>
     <row r="9" spans="1:23" ht="18" thickBot="1">
       <c r="A9" s="17"/>
-      <c r="B9" s="100" t="s">
+      <c r="B9" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="101"/>
-      <c r="D9" s="101"/>
-      <c r="E9" s="102"/>
+      <c r="C9" s="126"/>
+      <c r="D9" s="126"/>
+      <c r="E9" s="127"/>
       <c r="F9" s="18"/>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
@@ -9412,12 +9423,12 @@
     </row>
     <row r="10" spans="1:23" ht="56.25" customHeight="1" thickBot="1">
       <c r="A10" s="17"/>
-      <c r="B10" s="119" t="s">
+      <c r="B10" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="120"/>
-      <c r="D10" s="120"/>
-      <c r="E10" s="121"/>
+      <c r="C10" s="145"/>
+      <c r="D10" s="145"/>
+      <c r="E10" s="146"/>
       <c r="F10" s="16"/>
       <c r="G10" s="16"/>
       <c r="H10" s="16"/>
@@ -9438,12 +9449,12 @@
     </row>
     <row r="11" spans="1:23">
       <c r="A11" s="17"/>
-      <c r="B11" s="122" t="s">
+      <c r="B11" s="147" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="123"/>
-      <c r="D11" s="123"/>
-      <c r="E11" s="124"/>
+      <c r="C11" s="148"/>
+      <c r="D11" s="148"/>
+      <c r="E11" s="149"/>
       <c r="F11" s="16"/>
       <c r="G11" s="16"/>
       <c r="H11" s="16"/>
@@ -9464,10 +9475,10 @@
     </row>
     <row r="12" spans="1:23" ht="15" thickBot="1">
       <c r="A12" s="17"/>
-      <c r="B12" s="125"/>
-      <c r="C12" s="126"/>
-      <c r="D12" s="126"/>
-      <c r="E12" s="127"/>
+      <c r="B12" s="150"/>
+      <c r="C12" s="151"/>
+      <c r="D12" s="151"/>
+      <c r="E12" s="152"/>
       <c r="F12" s="16"/>
       <c r="G12" s="16"/>
       <c r="H12" s="16"/>
@@ -9859,12 +9870,12 @@
     </row>
     <row r="25" spans="1:22">
       <c r="A25" s="17"/>
-      <c r="B25" s="136" t="s">
+      <c r="B25" s="110" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="137"/>
-      <c r="D25" s="137"/>
-      <c r="E25" s="138"/>
+      <c r="C25" s="111"/>
+      <c r="D25" s="111"/>
+      <c r="E25" s="112"/>
       <c r="F25" s="16"/>
       <c r="G25" s="16"/>
       <c r="H25" s="16"/>
@@ -9885,10 +9896,10 @@
     </row>
     <row r="26" spans="1:22" ht="15" thickBot="1">
       <c r="A26" s="17"/>
-      <c r="B26" s="160"/>
-      <c r="C26" s="161"/>
-      <c r="D26" s="161"/>
-      <c r="E26" s="162"/>
+      <c r="B26" s="113"/>
+      <c r="C26" s="114"/>
+      <c r="D26" s="114"/>
+      <c r="E26" s="115"/>
       <c r="F26" s="16"/>
       <c r="G26" s="16"/>
       <c r="H26" s="16"/>
@@ -10053,12 +10064,12 @@
     </row>
     <row r="32" spans="1:22">
       <c r="A32" s="17"/>
-      <c r="B32" s="136" t="s">
+      <c r="B32" s="110" t="s">
         <v>27</v>
       </c>
-      <c r="C32" s="137"/>
-      <c r="D32" s="137"/>
-      <c r="E32" s="138"/>
+      <c r="C32" s="111"/>
+      <c r="D32" s="111"/>
+      <c r="E32" s="112"/>
       <c r="F32" s="16"/>
       <c r="G32" s="16"/>
       <c r="H32" s="16"/>
@@ -10079,10 +10090,10 @@
     </row>
     <row r="33" spans="1:22" ht="15" thickBot="1">
       <c r="A33" s="17"/>
-      <c r="B33" s="160"/>
-      <c r="C33" s="161"/>
-      <c r="D33" s="161"/>
-      <c r="E33" s="162"/>
+      <c r="B33" s="113"/>
+      <c r="C33" s="114"/>
+      <c r="D33" s="114"/>
+      <c r="E33" s="115"/>
       <c r="F33" s="16"/>
       <c r="G33" s="16"/>
       <c r="H33" s="16"/>
@@ -10112,7 +10123,7 @@
       <c r="D34" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="E34" s="164" t="s">
+      <c r="E34" s="166" t="s">
         <v>121</v>
       </c>
       <c r="F34" s="16"/>
@@ -10144,7 +10155,7 @@
       <c r="D35" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="E35" s="165"/>
+      <c r="E35" s="167"/>
       <c r="F35" s="16"/>
       <c r="G35" s="16"/>
       <c r="H35" s="16"/>
@@ -10174,7 +10185,7 @@
       <c r="D36" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="E36" s="166"/>
+      <c r="E36" s="168"/>
       <c r="F36" s="16"/>
       <c r="G36" s="16"/>
       <c r="H36" s="16"/>
@@ -10466,17 +10477,17 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="nw3c1yfVaD82UIKFAKDTKeHa7z+kBJe/zhWqIdLroB/gyinaj6cTGLKuRvfrkXUJqarD+MxxS2520gcCnBzYCQ==" saltValue="2qNKn9GiMKf3fTqjRE/FqQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="11">
+    <mergeCell ref="E34:E36"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B11:E12"/>
+    <mergeCell ref="B25:E26"/>
+    <mergeCell ref="B32:E33"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="B3:E6"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B8:E8"/>
-    <mergeCell ref="E34:E36"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B11:E12"/>
-    <mergeCell ref="B25:E26"/>
-    <mergeCell ref="B32:E33"/>
   </mergeCells>
   <conditionalFormatting sqref="B13:B19 D13:E19">
     <cfRule type="expression" dxfId="1" priority="1">
@@ -10495,21 +10506,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100659DA9939D4EAB4796CD11D35FA80828" ma:contentTypeVersion="1" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="280622034487628551932e19f9b67e4b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="72d2ce5a-7ad6-49a7-8fa5-8befc56c681c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="884e320e19264b04ef27a4dae7b7375b" ns2:_="">
     <xsd:import namespace="72d2ce5a-7ad6-49a7-8fa5-8befc56c681c"/>
@@ -10649,31 +10645,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CAB7335-583D-4882-A716-7A22D6BC7781}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="72d2ce5a-7ad6-49a7-8fa5-8befc56c681c"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B1CE4F8-7539-47AE-9669-AE32EB65884F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10733180-A130-4F70-A2A3-1A0B93CEDD9D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10689,4 +10676,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B1CE4F8-7539-47AE-9669-AE32EB65884F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CAB7335-583D-4882-A716-7A22D6BC7781}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="72d2ce5a-7ad6-49a7-8fa5-8befc56c681c"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>